--- a/GML2IFC/schema.xlsx
+++ b/GML2IFC/schema.xlsx
@@ -449,6 +449,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
@@ -470,6 +471,7 @@
         </is>
       </c>
     </row>
+    <row r="6"/>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
@@ -521,6 +523,7 @@
         </is>
       </c>
     </row>
+    <row r="10"/>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
@@ -805,10 +808,11 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>Pset_CityGMLAttributes</t>
-        </is>
-      </c>
-    </row>
+          <t>BEGEES_CityGMLAttributes</t>
+        </is>
+      </c>
+    </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
@@ -897,7 +901,6 @@
           <t>default (schema.json)</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -940,7 +943,6 @@
           <t>default (schema.json)</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -983,7 +985,6 @@
           <t>explicit (schema.json)</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1026,7 +1027,6 @@
           <t>explicit (schema.json)</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1069,7 +1069,6 @@
           <t>explicit (schema.json)</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1112,7 +1111,6 @@
           <t>explicit (schema.json)</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1155,7 +1153,6 @@
           <t>default (schema.json)</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1198,7 +1195,6 @@
           <t>default (schema.json)</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1241,7 +1237,6 @@
           <t>explicit (schema.json)</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1284,7 +1279,6 @@
           <t>explicit (schema.json)</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1327,7 +1321,6 @@
           <t>default (schema.json)</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1370,7 +1363,6 @@
           <t>default (schema.json)</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1413,7 +1405,6 @@
           <t>default (schema.json)</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1456,7 +1447,6 @@
           <t>default (schema.json)</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1499,7 +1489,6 @@
           <t>default (schema.json)</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1542,7 +1531,6 @@
           <t>default (schema.json)</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1585,7 +1573,6 @@
           <t>default (schema.json)</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1628,7 +1615,6 @@
           <t>default (schema.json)</t>
         </is>
       </c>
-      <c r="I21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1671,7 +1657,6 @@
           <t>default (schema.json)</t>
         </is>
       </c>
-      <c r="I22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1714,7 +1699,6 @@
           <t>default (schema.json)</t>
         </is>
       </c>
-      <c r="I23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1757,7 +1741,6 @@
           <t>default (schema.json)</t>
         </is>
       </c>
-      <c r="I24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1800,7 +1783,6 @@
           <t>default (schema.json)</t>
         </is>
       </c>
-      <c r="I25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1843,7 +1825,6 @@
           <t>default (schema.json)</t>
         </is>
       </c>
-      <c r="I26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1886,7 +1867,6 @@
           <t>default (schema.json)</t>
         </is>
       </c>
-      <c r="I27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -1929,7 +1909,6 @@
           <t>default (schema.json)</t>
         </is>
       </c>
-      <c r="I28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -1972,7 +1951,6 @@
           <t>default (schema.json)</t>
         </is>
       </c>
-      <c r="I29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -2015,7 +1993,6 @@
           <t>default (schema.json)</t>
         </is>
       </c>
-      <c r="I30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -2581,6 +2558,7 @@
         </is>
       </c>
     </row>
+    <row r="43"/>
     <row r="44">
       <c r="A44" s="4" t="inlineStr">
         <is>
@@ -2776,17 +2754,13 @@
         </is>
       </c>
     </row>
+    <row r="49"/>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
           <t>(anything else not listed above)</t>
         </is>
       </c>
-      <c r="B50" t="inlineStr"/>
-      <c r="C50" t="inlineStr"/>
-      <c r="D50" t="inlineStr"/>
-      <c r="E50" t="inlineStr"/>
-      <c r="F50" t="inlineStr"/>
       <c r="G50" t="inlineStr">
         <is>
           <t>IfcText</t>
@@ -2797,7 +2771,6 @@
           <t>default (schema.json)</t>
         </is>
       </c>
-      <c r="I50" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/GML2IFC/schema.xlsx
+++ b/GML2IFC/schema.xlsx
@@ -449,7 +449,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
@@ -471,7 +470,6 @@
         </is>
       </c>
     </row>
-    <row r="6"/>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
@@ -497,7 +495,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>CityGML element/class/function -&gt; IFC class</t>
+          <t>CityGML element/class/function -&gt; IFC class, for IFC 4.3 (default) and IFC4</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -523,7 +521,6 @@
         </is>
       </c>
     </row>
-    <row r="10"/>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
@@ -549,14 +546,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E8"/>
+  <dimension ref="A1:G8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
     <col width="26" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="38" customWidth="1" min="4" max="4"/>
-    <col width="55" customWidth="1" min="5" max="5"/>
+    <col width="24" customWidth="1" min="3" max="3"/>
+    <col width="44" customWidth="1" min="4" max="4"/>
+    <col width="44" customWidth="1" min="5" max="5"/>
+    <col width="44" customWidth="1" min="6" max="6"/>
+    <col width="55" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -572,15 +571,25 @@
       </c>
       <c r="C1" s="2" t="inlineStr">
         <is>
-          <t>IFC class</t>
+          <t>IFC class (4.3, default)</t>
         </is>
       </c>
       <c r="D1" s="2" t="inlineStr">
         <is>
-          <t>Spatial relation</t>
+          <t>Spatial relation (4.3)</t>
         </is>
       </c>
       <c r="E1" s="2" t="inlineStr">
+        <is>
+          <t>IFC class (IFC4, --ifc-version 4)</t>
+        </is>
+      </c>
+      <c r="F1" s="2" t="inlineStr">
+        <is>
+          <t>Spatial relation (IFC4)</t>
+        </is>
+      </c>
+      <c r="G1" s="2" t="inlineStr">
         <is>
           <t>Note / label</t>
         </is>
@@ -609,6 +618,16 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
+          <t>IfcBuilding</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>IfcRelAggregates (Site -&gt; Building)</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
           <t>LOD2 solid preferred, LOD0 footprint fallback (see module docstring)</t>
         </is>
       </c>
@@ -636,6 +655,16 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
+          <t>IfcWall</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>IfcRelContainedInSpatialStructure (Site -&gt; Element)</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
           <t>Mur (wall)</t>
         </is>
       </c>
@@ -663,6 +692,16 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
+          <t>IfcWall</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>IfcRelContainedInSpatialStructure (Site -&gt; Element)</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
           <t>Stödmur (retaining wall)</t>
         </is>
       </c>
@@ -690,6 +729,16 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
+          <t>IfcCivilElement (ObjectType=Road)</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>IfcRelContainedInSpatialStructure (Site -&gt; Element)</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
           <t>IfcFacility, aggregated into Site</t>
         </is>
       </c>
@@ -717,6 +766,16 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
+          <t>IfcCivilElement (ObjectType=Track)</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>IfcRelContainedInSpatialStructure (Site -&gt; Element)</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
           <t>CityGML 2.0 tran:Track = foot/cycle/horse path, not rail - mapped same as Road</t>
         </is>
       </c>
@@ -744,6 +803,16 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
+          <t>IfcCivilElement (ObjectType=TrafficArea)</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>IfcRelContainedInSpatialStructure (Site -&gt; Element)</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
           <t>plain IfcElement, contained in Site</t>
         </is>
       </c>
@@ -770,6 +839,16 @@
         </is>
       </c>
       <c r="E8" t="inlineStr">
+        <is>
+          <t>IfcCivilElement</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>IfcRelContainedInSpatialStructure (Site -&gt; Element)</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
         <is>
           <t>original CityGML element tag kept as 'citygmlType' Pset attribute</t>
         </is>
@@ -812,7 +891,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
@@ -2558,7 +2636,6 @@
         </is>
       </c>
     </row>
-    <row r="43"/>
     <row r="44">
       <c r="A44" s="4" t="inlineStr">
         <is>
@@ -2754,7 +2831,6 @@
         </is>
       </c>
     </row>
-    <row r="49"/>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
